--- a/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_ขลุง_ปีงบ69.xlsx
+++ b/Dashboard_GIS/ข้อมูลดิบ/แรงดันน้ำ/PRESSURE_ขลุง_ปีงบ69.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Report" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$M$60</definedName>
+    <definedName function="false" hidden="false" name="__bookmark_1" vbProcedure="false">Report!$A$4:$N$60</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t xml:space="preserve">รายงานการตรวจวัดค่าแรงดันน้ำ</t>
   </si>
@@ -322,6 +322,48 @@
         <family val="2"/>
         <charset val="222"/>
       </rPr>
+      <t xml:space="preserve">เม</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">ย</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
+      <t xml:space="preserve">. 69</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="222"/>
+      </rPr>
       <t xml:space="preserve">ก</t>
     </r>
     <r>
@@ -4173,7 +4215,7 @@
     <t xml:space="preserve">พิมพ์รายงานวันที่</t>
   </si>
   <si>
-    <t xml:space="preserve">4/3/2569</t>
+    <t xml:space="preserve">3/4/2569</t>
   </si>
   <si>
     <t xml:space="preserve">หน้าที่</t>
@@ -4386,7 +4428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr defaultColWidth="11.74609375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.6"/>
@@ -4400,15 +4442,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="1.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="5.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="1.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="5.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="0.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="2.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="6.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="1.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="5.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="7.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="0.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="2.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,11 +4473,12 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
@@ -4455,11 +4499,12 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="3"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -4480,11 +4525,12 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -4500,6 +4546,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
@@ -4534,6 +4581,9 @@
       </c>
       <c r="M5" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4550,13 +4600,14 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -4580,9 +4631,12 @@
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4591,7 +4645,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -4615,9 +4669,12 @@
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4626,7 +4683,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -4650,9 +4707,12 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4661,7 +4721,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4685,9 +4745,12 @@
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4696,7 +4759,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -4720,9 +4783,12 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4731,7 +4797,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -4755,9 +4821,12 @@
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4766,7 +4835,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -4790,9 +4859,12 @@
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4801,7 +4873,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -4825,9 +4897,12 @@
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4836,7 +4911,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -4860,9 +4935,12 @@
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4871,7 +4949,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -4895,9 +4973,12 @@
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4906,7 +4987,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -4930,9 +5011,12 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4941,7 +5025,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -4965,9 +5049,12 @@
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4976,7 +5063,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -5000,9 +5087,12 @@
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5011,7 +5101,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -5035,9 +5125,12 @@
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5046,7 +5139,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -5070,9 +5163,12 @@
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5081,7 +5177,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -5105,9 +5201,12 @@
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5116,7 +5215,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -5140,9 +5239,12 @@
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5151,7 +5253,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -5175,9 +5277,12 @@
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5186,7 +5291,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -5210,9 +5315,12 @@
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5221,7 +5329,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -5245,9 +5353,12 @@
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5256,7 +5367,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
@@ -5280,9 +5391,12 @@
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5291,7 +5405,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -5315,9 +5429,12 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5326,7 +5443,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -5350,9 +5467,12 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5361,7 +5481,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -5385,9 +5505,12 @@
       </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5396,7 +5519,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -5420,9 +5543,12 @@
       </c>
       <c r="K31" s="9"/>
       <c r="L31" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5431,7 +5557,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5455,9 +5581,12 @@
       </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5466,7 +5595,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
@@ -5490,9 +5619,12 @@
       </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5501,7 +5633,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -5525,9 +5657,12 @@
       </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5536,7 +5671,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
@@ -5560,9 +5695,12 @@
       </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5571,7 +5709,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
@@ -5595,9 +5733,12 @@
       </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5606,7 +5747,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -5630,9 +5771,12 @@
       </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5641,7 +5785,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
@@ -5665,9 +5809,12 @@
       </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5676,7 +5823,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -5700,9 +5847,12 @@
       </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5711,7 +5861,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -5735,9 +5885,12 @@
       </c>
       <c r="K40" s="9"/>
       <c r="L40" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5746,7 +5899,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -5770,9 +5923,12 @@
       </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5781,7 +5937,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -5805,9 +5961,12 @@
       </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5816,7 +5975,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
@@ -5840,9 +5999,12 @@
       </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5851,7 +6013,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -5875,9 +6037,12 @@
       </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5886,7 +6051,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -5910,9 +6075,12 @@
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5921,7 +6089,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
@@ -5945,9 +6113,12 @@
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5956,7 +6127,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -5980,9 +6151,12 @@
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5991,7 +6165,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -6015,9 +6189,12 @@
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6026,7 +6203,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -6050,9 +6227,12 @@
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6061,7 +6241,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -6085,9 +6265,12 @@
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6096,7 +6279,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
@@ -6120,9 +6303,12 @@
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6131,7 +6317,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -6155,9 +6341,12 @@
       </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6166,7 +6355,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -6190,9 +6379,12 @@
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6201,7 +6393,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
@@ -6225,9 +6417,12 @@
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6236,7 +6431,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -6260,9 +6455,12 @@
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6271,7 +6469,7 @@
         <v>50</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
@@ -6295,9 +6493,12 @@
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6306,7 +6507,7 @@
         <v>51</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
@@ -6330,9 +6531,12 @@
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6341,7 +6545,7 @@
         <v>52</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -6365,9 +6569,12 @@
       </c>
       <c r="K58" s="9"/>
       <c r="L58" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6376,7 +6583,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -6400,9 +6607,12 @@
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6411,7 +6621,7 @@
         <v>54</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
@@ -6435,9 +6645,12 @@
       </c>
       <c r="K60" s="9"/>
       <c r="L60" s="9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6464,10 +6677,11 @@
       <c r="T61" s="10"/>
       <c r="U61" s="10"/>
       <c r="V61" s="10"/>
+      <c r="W61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
@@ -6479,7 +6693,7 @@
       <c r="I62" s="11"/>
       <c r="J62" s="11"/>
       <c r="K62" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="11"/>
@@ -6492,10 +6706,11 @@
       <c r="T62" s="11"/>
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
+      <c r="W62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -6507,7 +6722,7 @@
       <c r="I63" s="11"/>
       <c r="J63" s="11"/>
       <c r="K63" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L63" s="11"/>
       <c r="M63" s="11"/>
@@ -6520,10 +6735,11 @@
       <c r="T63" s="11"/>
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
+      <c r="W63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -6535,7 +6751,7 @@
       <c r="I64" s="12"/>
       <c r="J64" s="12"/>
       <c r="K64" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="12"/>
@@ -6548,6 +6764,7 @@
       <c r="T64" s="12"/>
       <c r="U64" s="12"/>
       <c r="V64" s="12"/>
+      <c r="W64" s="12"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13"/>
@@ -6561,39 +6778,40 @@
       <c r="I65" s="10"/>
       <c r="J65" s="10"/>
       <c r="K65" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L65" s="13"/>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
-      <c r="O65" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="P65" s="13" t="s">
+      <c r="O65" s="13"/>
+      <c r="P65" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="Q65" s="13"/>
-      <c r="R65" s="15" t="s">
+      <c r="Q65" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="S65" s="12" t="s">
+      <c r="R65" s="13"/>
+      <c r="S65" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="T65" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="U65" s="10"/>
+      <c r="T65" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="U65" s="14" t="s">
+        <v>75</v>
+      </c>
       <c r="V65" s="10"/>
+      <c r="W65" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="134">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:P1"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="C2:Q2"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="C3:Q3"/>
+    <mergeCell ref="R3:V3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B5:D5"/>
@@ -6709,18 +6927,18 @@
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="J60:K60"/>
     <mergeCell ref="A61:J61"/>
-    <mergeCell ref="K61:V61"/>
+    <mergeCell ref="K61:W61"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="K62:V62"/>
+    <mergeCell ref="K62:W62"/>
     <mergeCell ref="A63:J63"/>
-    <mergeCell ref="K63:V63"/>
+    <mergeCell ref="K63:W63"/>
     <mergeCell ref="A64:J64"/>
-    <mergeCell ref="K64:V64"/>
+    <mergeCell ref="K64:W64"/>
     <mergeCell ref="A65:C65"/>
     <mergeCell ref="D65:J65"/>
-    <mergeCell ref="K65:N65"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="K65:O65"/>
+    <mergeCell ref="Q65:R65"/>
+    <mergeCell ref="V65:W65"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
